--- a/output/pdf_financials_xlsx/ELEF.xlsx
+++ b/output/pdf_financials_xlsx/ELEF.xlsx
@@ -6723,34 +6723,34 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.582419</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>17.138468</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>18.577859</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>19.790089</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>20.502885</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>21.205698</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>21.482133</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>22621.202</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>23413.83</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>24058.336</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -6758,19 +6758,19 @@
         </is>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>26.335247</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>28.958228</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>28.740877</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>28.678391</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>29.359167</v>
       </c>
     </row>
     <row r="93">
@@ -12010,7 +12010,11 @@
           <t>Reserves (note 14)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -14474,7 +14478,11 @@
           <t>Reserves (note 16)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -18296,7 +18304,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -19446,7 +19458,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -27506,7 +27522,11 @@
           <t>Reserves 17,138,468</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ELEF.xlsx
+++ b/output/pdf_financials_xlsx/ELEF.xlsx
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009398999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.135466</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.059435</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.02889</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.01648</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2250,20 +2250,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P26" s="3" t="n">
+        <v>26.454938</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>32.593257</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>36.960228</v>
       </c>
       <c r="S26" s="1" t="inlineStr">
         <is>
@@ -2298,13 +2292,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-61.389108</v>
+        <v>-61.448543</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-23.296154</v>
+        <v>-23.325044</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-14.696041</v>
+        <v>-14.712521</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-7.822531</v>
@@ -2440,13 +2434,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-61.389108</v>
+        <v>-61.448543</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-23.158619</v>
+        <v>-23.187509</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-14.608607</v>
+        <v>-14.625087</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-7.822531</v>
@@ -2800,7 +2794,7 @@
         <v>0.200994</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.033542</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.021648</v>
@@ -2820,19 +2814,19 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.378693</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.504969</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.209099</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.271838</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.324948</v>
       </c>
     </row>
     <row r="35">
@@ -2934,7 +2928,7 @@
         <v>0.200994</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.033542</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.197648</v>
@@ -2954,19 +2948,19 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.378693</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.504969</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.209099</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.271838</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.324948</v>
       </c>
     </row>
     <row r="37">
@@ -3738,7 +3732,7 @@
         <v>0.732082</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.2368</v>
+        <v>0.203258</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.200526</v>
@@ -3758,19 +3752,19 @@
         </is>
       </c>
       <c r="O48" s="3" t="n">
-        <v>8.198031</v>
+        <v>6.819338</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.918525</v>
+        <v>0.413556</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.493791</v>
+        <v>0.284692</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.339838</v>
+        <v>0.068</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.440313</v>
+        <v>0.115365</v>
       </c>
     </row>
     <row r="49">
@@ -8896,25 +8890,25 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-36.528</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.037162</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022939</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013974</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.021855</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023145</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0204</v>
       </c>
     </row>
     <row r="125">
@@ -8965,25 +8959,25 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-36.528</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.037162</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022939</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013974</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.021855</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023145</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0204</v>
       </c>
     </row>
     <row r="126">
@@ -9854,7 +9848,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17102,7 +17096,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -19756,7 +19754,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -20178,7 +20176,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -26350,7 +26348,11 @@
           <t>Reclamation deposits 6,500</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -31986,7 +31988,11 @@
           <t>Lease payments (note 10)</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -35774,7 +35780,11 @@
           <t>Lease payments (note 12)</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -38200,7 +38210,11 @@
           <t>Lease payments (note 11)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -39784,7 +39798,11 @@
           <t>Prepaid expenses and reclamation deposits</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -41358,7 +41376,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -45160,7 +45182,11 @@
           <t>Prepaid expenses and reclamation deposits</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -46366,7 +46392,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -61318,7 +61348,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -75098,7 +75128,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -78286,7 +78316,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -79726,7 +79756,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -80362,7 +80392,7 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -83616,7 +83646,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -85716,7 +85746,7 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E730" t="inlineStr">

--- a/output/pdf_financials_xlsx/ELEF.xlsx
+++ b/output/pdf_financials_xlsx/ELEF.xlsx
@@ -8050,10 +8050,10 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>2.924982</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.012331</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -47538,7 +47538,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ELEF.xlsx
+++ b/output/pdf_financials_xlsx/ELEF.xlsx
@@ -819,49 +819,49 @@
         <v>1.481388</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.995744</v>
+        <v>2.126196</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.619785</v>
+        <v>1.955749</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.526233</v>
+        <v>0.773888</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.447796</v>
+        <v>0.599619</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.519258</v>
+        <v>0.61326</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.390789</v>
+        <v>0.454029</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>893.986</v>
+        <v>954.586</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>448.445</v>
+        <v>518.823</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>469.117</v>
+        <v>572.922</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.807578</v>
+        <v>0.916178</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.130955</v>
+        <v>1.250756</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.872932</v>
+        <v>2.179366</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.656</v>
+        <v>1.878778</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.896701</v>
+        <v>1.039501</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.770798</v>
+        <v>0.889398</v>
       </c>
     </row>
     <row r="8">
@@ -1014,10 +1014,10 @@
         <v>2.427869</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.639568</v>
+        <v>3.77002</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5.364631</v>
+        <v>5.700595</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>4.094448</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-61.389108</v>
+        <v>-72.237385</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-23.296154</v>
+        <v>-22.343054</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-14.696041</v>
@@ -1498,16 +1498,16 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>4.62956</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>12.959668</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>10.848277</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-61.448543</v>
+        <v>-72.29682</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-23.325044</v>
+        <v>-22.371944</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-14.712521</v>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-61.448543</v>
+        <v>-72.29682</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-23.187509</v>
+        <v>-22.234409</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-14.625087</v>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-15.01753835635108</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.26575525440703</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -5032,27 +5032,25 @@
         <v>1.432238</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.43048</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.433884</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>250.988</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N67" s="3" t="n">
+        <v>41.186</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -7996,13 +7994,13 @@
         <v>-113.564</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.111592</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.625619</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -8206,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P114" s="3" t="n">
         <v>0</v>
@@ -9611,13 +9609,13 @@
         <v>-113.564</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.111592</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.625619</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -9680,13 +9678,13 @@
         <v>-3222.939</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-2.549042</v>
+        <v>-2.660634</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-2.19116</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-6.330557</v>
+        <v>-6.956176</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-0.260081</v>
@@ -31674,7 +31672,11 @@
           <t>Proceeds from share issuances (note 14(b))</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -35256,7 +35258,11 @@
           <t>Proceeds from share issuances (note 16(b))</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -37266,7 +37272,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -40222,7 +40232,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -55864,7 +55878,11 @@
           <t>Directors fees (note 16)</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -58866,7 +58884,11 @@
           <t>Director fees (note 18)</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -73564,7 +73586,11 @@
           <t>Director fees 23</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
@@ -76666,7 +76692,11 @@
           <t>Director fees 22</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr"/>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E643" t="inlineStr">
         <is>
           <t>-</t>
@@ -79246,7 +79276,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr"/>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E668" t="inlineStr">
         <is>
           <t>-</t>
@@ -80912,7 +80946,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E684" t="inlineStr">
         <is>
           <t>-</t>
@@ -82596,7 +82634,11 @@
           <t>Loss Before Other Items and Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E700" t="inlineStr">
         <is>
           <t>-</t>
@@ -84284,7 +84326,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E716" t="inlineStr">
         <is>
           <t>-</t>
@@ -86598,7 +86644,11 @@
           <t>Loss Before Deferred Income Tax Recovery (Expense)</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E738" t="inlineStr">
         <is>
           <t>-</t>
@@ -86702,7 +86752,11 @@
           <t>Deferred income tax recovery (expense) 21</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E739" t="inlineStr">
         <is>
           <t>-</t>
@@ -87228,7 +87282,11 @@
           <t>Loss Before Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D744" t="inlineStr"/>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E744" t="inlineStr">
         <is>
           <t>-</t>
@@ -87332,7 +87390,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E745" t="inlineStr">
         <is>
           <t>-</t>
